--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -526,13 +526,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-15 09:27:46</t>
+          <t>2026-08-15 17:35:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -544,13 +544,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-15 09:23:01</t>
+          <t>2026-08-15 16:08:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -562,13 +562,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-15 09:02:29</t>
+          <t>2026-08-15 09:27:46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -580,13 +580,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-15 08:47:08</t>
+          <t>2026-08-15 09:23:01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -598,13 +598,13 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-15 08:42:00</t>
+          <t>2026-08-15 09:02:29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -616,13 +616,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-15 08:41:07</t>
+          <t>2026-08-15 08:47:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -634,13 +634,13 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-15 08:38:32</t>
+          <t>2026-08-15 08:42:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -652,13 +652,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-15 08:21:13</t>
+          <t>2026-08-15 08:41:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -669,6 +669,42 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-15 08:38:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-15 08:21:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-08-15 08:17:32</t>
         </is>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -526,187 +526,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-15 17:35:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-08-15 16:08:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-08-15 09:27:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-15 09:23:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-15 09:02:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-08-15 08:47:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-15 08:42:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-08-15 08:41:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-08-15 08:38:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-08-15 08:21:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>317madhavgarg@gmail.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-08-15 08:17:32</t>
+          <t>2026-08-16 10:34:08</t>
         </is>
       </c>
     </row>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -442,7 +442,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-15 09:04:03</t>
+          <t>2026-08-16 10:45:25</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -514,17 +514,197 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:01:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:59:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:50:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:50:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>14</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-08-16 10:34:08</t>
         </is>
@@ -541,12 +721,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,6 +747,26 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:04:03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-16 16:14:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -415,11 +415,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -442,29 +442,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:25</t>
+          <t>2026-08-16 11:56:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2026-08-15 08:10:48</t>
         </is>
@@ -481,12 +496,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -514,133 +529,133 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:36</t>
+          <t>2026-08-16 11:59:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:04</t>
+          <t>2026-08-16 11:59:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-16 10:59:04</t>
+          <t>2026-08-16 11:56:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16 10:58:32</t>
+          <t>2026-08-16 11:56:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:54</t>
+          <t>2026-08-16 11:56:14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:25</t>
+          <t>2026-08-16 11:51:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:38</t>
+          <t>2026-08-16 11:49:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
@@ -652,13 +667,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:12</t>
+          <t>2026-08-16 11:47:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
@@ -670,31 +685,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:36</t>
+          <t>2026-08-16 11:43:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16 10:44:40</t>
+          <t>2026-08-16 11:01:36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -705,6 +720,168 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:01:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:59:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:50:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:50:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>2026-08-16 10:34:08</t>
         </is>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,43 +529,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:15</t>
+          <t>2026-08-16 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:03</t>
+          <t>2026-08-16 12:26:14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -577,13 +577,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:57</t>
+          <t>2026-08-16 12:22:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
@@ -595,13 +595,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:37</t>
+          <t>2026-08-16 11:59:15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" t="n">
         <v>4</v>
@@ -613,13 +613,13 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:14</t>
+          <t>2026-08-16 11:59:03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B7" t="n">
         <v>3</v>
@@ -631,49 +631,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16 11:51:08</t>
+          <t>2026-08-16 11:56:57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16 11:49:29</t>
+          <t>2026-08-16 11:56:37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16 11:47:07</t>
+          <t>2026-08-16 11:56:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
@@ -685,13 +685,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16 11:43:25</t>
+          <t>2026-08-16 11:51:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -703,49 +703,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:36</t>
+          <t>2026-08-16 11:49:29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:04</t>
+          <t>2026-08-16 11:47:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-16 10:59:04</t>
+          <t>2026-08-16 11:43:25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -757,31 +757,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-16 10:58:32</t>
+          <t>2026-08-16 11:01:36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:54</t>
+          <t>2026-08-16 11:01:04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -793,31 +793,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:25</t>
+          <t>2026-08-16 10:59:04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:38</t>
+          <t>2026-08-16 10:58:32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n">
         <v>3</v>
@@ -829,31 +829,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:12</t>
+          <t>2026-08-16 10:50:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:36</t>
+          <t>2026-08-16 10:50:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
@@ -865,23 +865,77 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-16 10:44:40</t>
+          <t>2026-08-16 10:46:38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>14</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B24" t="n">
         <v>1</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2026-08-16 10:34:08</t>
         </is>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -415,11 +415,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -442,29 +442,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>bansallovish843@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:25</t>
+          <t>2026-08-16 13:21:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>harshilagarwal15@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:43:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2026-08-15 08:10:48</t>
         </is>
@@ -481,12 +511,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -514,7 +544,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B2" t="n">
         <v>3</v>
@@ -526,121 +556,121 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:36</t>
+          <t>2026-08-16 13:26:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:04</t>
+          <t>2026-08-16 11:56:24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-16 10:59:04</t>
+          <t>2026-08-16 11:50:50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16 10:58:32</t>
+          <t>2026-08-16 11:50:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:54</t>
+          <t>2026-08-16 11:47:03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:25</t>
+          <t>2026-08-16 11:44:43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:38</t>
+          <t>2026-08-16 11:44:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
@@ -652,13 +682,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:12</t>
+          <t>2026-08-16 11:39:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
@@ -670,13 +700,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:36</t>
+          <t>2026-08-16 11:01:36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -688,13 +718,13 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16 10:44:40</t>
+          <t>2026-08-16 11:01:04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -705,6 +735,150 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:59:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:50:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:50:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>2026-08-16 10:34:08</t>
         </is>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n">
         <v>3</v>
@@ -541,13 +541,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16 12:28:57</t>
+          <t>2026-08-16 13:11:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
@@ -559,13 +559,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-16 12:26:14</t>
+          <t>2026-08-16 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -577,31 +577,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-16 12:22:08</t>
+          <t>2026-08-16 12:26:14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:15</t>
+          <t>2026-08-16 12:22:08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="n">
         <v>4</v>
@@ -613,49 +613,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:03</t>
+          <t>2026-08-16 11:59:15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:57</t>
+          <t>2026-08-16 11:59:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:37</t>
+          <t>2026-08-16 11:56:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="n">
         <v>4</v>
@@ -667,31 +667,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:14</t>
+          <t>2026-08-16 11:56:37</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16 11:51:08</t>
+          <t>2026-08-16 11:56:14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -703,13 +703,13 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16 11:49:29</t>
+          <t>2026-08-16 11:51:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -721,13 +721,13 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-16 11:47:07</t>
+          <t>2026-08-16 11:49:29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
@@ -739,13 +739,13 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-16 11:43:25</t>
+          <t>2026-08-16 11:47:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -757,31 +757,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:36</t>
+          <t>2026-08-16 11:43:25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:04</t>
+          <t>2026-08-16 11:01:36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -793,31 +793,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-16 10:59:04</t>
+          <t>2026-08-16 11:01:04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-16 10:58:32</t>
+          <t>2026-08-16 10:59:04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" t="n">
         <v>3</v>
@@ -829,31 +829,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:54</t>
+          <t>2026-08-16 10:58:32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:25</t>
+          <t>2026-08-16 10:50:54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
@@ -865,31 +865,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:38</t>
+          <t>2026-08-16 10:50:25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:12</t>
+          <t>2026-08-16 10:46:38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B22" t="n">
         <v>3</v>
@@ -901,31 +901,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:36</t>
+          <t>2026-08-16 10:46:12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-16 10:44:40</t>
+          <t>2026-08-16 10:45:36</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
@@ -936,6 +936,24 @@
         </is>
       </c>
       <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>2026-08-16 10:34:08</t>
         </is>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="n">
         <v>3</v>
@@ -541,13 +541,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16 13:11:43</t>
+          <t>2026-08-16 13:58:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
@@ -559,13 +559,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-16 12:28:57</t>
+          <t>2026-08-16 13:11:43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -577,13 +577,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-16 12:26:14</t>
+          <t>2026-08-16 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
@@ -595,31 +595,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16 12:22:08</t>
+          <t>2026-08-16 12:26:14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:15</t>
+          <t>2026-08-16 12:22:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
@@ -631,49 +631,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:03</t>
+          <t>2026-08-16 11:59:15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:57</t>
+          <t>2026-08-16 11:59:03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:37</t>
+          <t>2026-08-16 11:56:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="n">
         <v>4</v>
@@ -685,31 +685,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:14</t>
+          <t>2026-08-16 11:56:37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16 11:51:08</t>
+          <t>2026-08-16 11:56:14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -721,13 +721,13 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-16 11:49:29</t>
+          <t>2026-08-16 11:51:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
@@ -739,13 +739,13 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-16 11:47:07</t>
+          <t>2026-08-16 11:49:29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -757,13 +757,13 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-16 11:43:25</t>
+          <t>2026-08-16 11:47:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
@@ -775,31 +775,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:36</t>
+          <t>2026-08-16 11:43:25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:04</t>
+          <t>2026-08-16 11:01:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -811,31 +811,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-16 10:59:04</t>
+          <t>2026-08-16 11:01:04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-16 10:58:32</t>
+          <t>2026-08-16 10:59:04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
@@ -847,31 +847,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:54</t>
+          <t>2026-08-16 10:58:32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:25</t>
+          <t>2026-08-16 10:50:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
@@ -883,31 +883,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:38</t>
+          <t>2026-08-16 10:50:25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:12</t>
+          <t>2026-08-16 10:46:38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" t="n">
         <v>3</v>
@@ -919,31 +919,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:36</t>
+          <t>2026-08-16 10:46:12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-16 10:44:40</t>
+          <t>2026-08-16 10:45:36</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
@@ -954,6 +954,24 @@
         </is>
       </c>
       <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026-08-16 10:34:08</t>
         </is>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -442,44 +442,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>codexproject9@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:11</t>
+          <t>2026-08-16 14:27:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:25</t>
+          <t>2026-08-16 11:56:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2026-08-15 08:10:48</t>
         </is>
@@ -496,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,7 +544,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B2" t="n">
         <v>3</v>
@@ -541,31 +556,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16 13:58:25</t>
+          <t>2026-08-16 14:28:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>codexproject9@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-16 13:11:43</t>
+          <t>2026-08-16 14:27:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -577,31 +592,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-16 12:28:57</t>
+          <t>2026-08-16 14:25:37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16 12:26:14</t>
+          <t>2026-08-16 14:24:46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
@@ -613,49 +628,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16 12:22:08</t>
+          <t>2026-08-16 13:58:25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:15</t>
+          <t>2026-08-16 13:11:43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:03</t>
+          <t>2026-08-16 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
@@ -667,31 +682,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:57</t>
+          <t>2026-08-16 12:26:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>harshilagarwal15@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:37</t>
+          <t>2026-08-16 12:22:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
@@ -703,31 +718,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:14</t>
+          <t>2026-08-16 11:59:15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-16 11:51:08</t>
+          <t>2026-08-16 11:59:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
@@ -739,49 +754,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-16 11:49:29</t>
+          <t>2026-08-16 11:56:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-16 11:47:07</t>
+          <t>2026-08-16 11:56:37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-16 11:43:25</t>
+          <t>2026-08-16 11:56:14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
@@ -793,49 +808,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:36</t>
+          <t>2026-08-16 11:51:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:04</t>
+          <t>2026-08-16 11:49:29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-16 10:59:04</t>
+          <t>2026-08-16 11:47:07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
@@ -847,13 +862,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-16 10:58:32</t>
+          <t>2026-08-16 11:43:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B20" t="n">
         <v>3</v>
@@ -865,13 +880,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:54</t>
+          <t>2026-08-16 11:01:36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
@@ -883,13 +898,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:25</t>
+          <t>2026-08-16 11:01:04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -901,13 +916,13 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:38</t>
+          <t>2026-08-16 10:59:04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
         <v>3</v>
@@ -919,13 +934,13 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:12</t>
+          <t>2026-08-16 10:58:32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
@@ -937,13 +952,13 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:36</t>
+          <t>2026-08-16 10:50:54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
@@ -955,13 +970,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-16 10:44:40</t>
+          <t>2026-08-16 10:50:25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -972,6 +987,78 @@
         </is>
       </c>
       <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>14</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026-08-16 10:34:08</t>
         </is>

--- a/users_data.xlsx
+++ b/users_data.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,97 +529,97 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16 13:58:25</t>
+          <t>2026-08-21 17:31:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-16 13:11:43</t>
+          <t>2026-08-21 17:29:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-16 12:28:57</t>
+          <t>2026-08-21 17:25:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16 12:26:14</t>
+          <t>2026-08-21 17:23:22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16 12:22:08</t>
+          <t>2026-08-21 17:06:43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
@@ -631,13 +631,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:15</t>
+          <t>2026-08-21 17:05:52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -649,31 +649,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16 11:59:03</t>
+          <t>2026-08-21 17:03:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:57</t>
+          <t>2026-08-21 16:33:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B10" t="n">
         <v>4</v>
@@ -685,13 +685,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:37</t>
+          <t>2026-08-21 16:26:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
@@ -703,211 +703,211 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16 11:56:14</t>
+          <t>2026-08-21 16:21:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-16 11:51:08</t>
+          <t>2026-08-21 16:17:40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-16 11:49:29</t>
+          <t>2026-08-21 16:15:40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-16 11:47:07</t>
+          <t>2026-08-21 16:14:14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-16 11:43:25</t>
+          <t>2026-08-21 16:01:45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:36</t>
+          <t>2026-08-21 16:00:15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-16 11:01:04</t>
+          <t>2026-08-21 15:58:12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-16 10:59:04</t>
+          <t>2026-08-21 15:28:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-16 10:58:32</t>
+          <t>2026-08-21 14:14:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pgarg_be24@thapar.edu</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:54</t>
+          <t>2026-08-21 14:12:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-16 10:50:25</t>
+          <t>2026-08-21 14:04:59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>harshilagarwal15@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:38</t>
+          <t>2026-08-21 14:03:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B23" t="n">
         <v>3</v>
@@ -919,13 +919,13 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-16 10:46:12</t>
+          <t>2026-08-16 13:58:25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
@@ -937,41 +937,419 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-16 10:45:36</t>
+          <t>2026-08-16 13:11:43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>317madhavgarg@gmail.com</t>
+          <t>pgarg_be24@thapar.edu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-16 10:44:40</t>
+          <t>2026-08-16 12:28:57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>36</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-16 12:26:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>35</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-16 12:22:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>harshilagarwal15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:59:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>33</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>harshilagarwal15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:59:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>32</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>31</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>harshilagarwal15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:56:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>harshilagarwal15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:56:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>28</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:49:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:47:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>26</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:43:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>24</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-16 11:01:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>23</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:59:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>22</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>21</v>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:50:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>20</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:50:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>19</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>18</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:46:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>17</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>pgarg_be24@thapar.edu</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:45:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>16</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>317madhavgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>14</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B47" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>317madhavgarg@gmail.com</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2026-08-16 10:34:08</t>
         </is>
